--- a/templates/Ho_So_KCS_QS_TienDo_Nha_Dan_Dung.xlsx
+++ b/templates/Ho_So_KCS_QS_TienDo_Nha_Dan_Dung.xlsx
@@ -592,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L19"/>
+  <dimension ref="A2:L19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -609,7 +609,6 @@
     <col width="17" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -624,7 +623,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
@@ -1282,7 +1280,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L28"/>
+  <dimension ref="A2:L28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -1299,7 +1297,6 @@
     <col width="30" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -1314,7 +1311,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
@@ -2176,7 +2172,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L30"/>
+  <dimension ref="A2:L30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="65" customWidth="1" min="1" max="1"/>
@@ -2193,7 +2189,6 @@
     <col width="22" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -2208,7 +2203,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
@@ -3128,7 +3122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A2:L25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -3145,7 +3139,6 @@
     <col width="46" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -3160,7 +3153,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
@@ -4001,7 +3993,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L14"/>
+  <dimension ref="A2:L14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -4018,7 +4010,6 @@
     <col width="24" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -4033,7 +4024,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
@@ -4454,7 +4444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A2:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -4464,7 +4454,6 @@
     <col width="20" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -4479,7 +4468,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
@@ -4836,7 +4824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M31"/>
+  <dimension ref="A2:M31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -4854,7 +4842,6 @@
     <col width="18" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -4869,7 +4856,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
@@ -6334,7 +6320,7 @@
         <v>0</v>
       </c>
       <c r="I31" s="6">
-        <f>ROUNDUP(G31/H31, 0)</f>
+        <f>IF(H31=0, 0, ROUNDUP(G31/H31, 0))</f>
         <v/>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -6375,7 +6361,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A2:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -6387,7 +6373,6 @@
     <col width="45" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -6402,7 +6387,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
